--- a/data/seeds/document_master_default.xlsx
+++ b/data/seeds/document_master_default.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="documents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="documents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG261"/>
+  <dimension ref="A1:AI266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,16 @@
           <t>completed_by</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>importance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -713,6 +723,8 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -844,6 +856,8 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -975,6 +989,8 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1106,6 +1122,8 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1237,6 +1255,8 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1368,6 +1388,8 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1499,6 +1521,8 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1630,6 +1654,8 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1761,6 +1787,8 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1892,6 +1920,8 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1946,7 +1976,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>未整備</t>
+          <t>整備済</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2001,7 +2031,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-04 12:00:00</t>
+          <t>2026-05-05 09:30:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,10 +2049,24 @@
           <t>ひな形パス反映済み／マスタ整合性整理済み</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>media/documents/completed/DOC-GOV-011_20260505_093037.docx</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>短時間正社員、育児以外でも_日経 4月27日.docx</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:30:37</t>
+        </is>
+      </c>
       <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2154,6 +2198,8 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2285,6 +2331,8 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2416,6 +2464,8 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2547,6 +2597,8 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2678,6 +2730,8 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2809,6 +2863,8 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2940,6 +2996,8 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3071,6 +3129,8 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3202,6 +3262,8 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3329,6 +3391,8 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3456,6 +3520,8 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3583,6 +3649,8 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3710,6 +3778,8 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3837,6 +3907,8 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3964,6 +4036,8 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4091,6 +4165,8 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4218,6 +4294,8 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4345,6 +4423,8 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4472,6 +4552,8 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4599,6 +4681,8 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4726,6 +4810,8 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4853,6 +4939,8 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4980,6 +5068,8 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5103,6 +5193,8 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5226,6 +5318,8 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5349,6 +5443,8 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5472,6 +5568,8 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5595,6 +5693,8 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5722,6 +5822,8 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5849,6 +5951,8 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5976,6 +6080,8 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6103,6 +6209,8 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6230,6 +6338,8 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6357,6 +6467,8 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6484,6 +6596,8 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6611,6 +6725,8 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6738,6 +6854,8 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6865,6 +6983,8 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6992,6 +7112,8 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7119,6 +7241,8 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7246,6 +7370,8 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7373,6 +7499,8 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7500,6 +7628,8 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7627,6 +7757,8 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7754,6 +7886,8 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7881,6 +8015,8 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8004,6 +8140,8 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8127,6 +8265,8 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8250,6 +8390,8 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8377,6 +8519,8 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8504,6 +8648,8 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8631,6 +8777,8 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8758,6 +8906,8 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8885,6 +9035,8 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9012,6 +9164,8 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9139,6 +9293,8 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9266,6 +9422,8 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9393,6 +9551,8 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9520,6 +9680,8 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9647,6 +9809,8 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9774,6 +9938,8 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9901,6 +10067,8 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10028,6 +10196,8 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10155,6 +10325,8 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10282,6 +10454,8 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10409,6 +10583,8 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10536,6 +10712,8 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10663,6 +10841,8 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10790,6 +10970,8 @@
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10921,6 +11103,8 @@
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11052,6 +11236,8 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11183,6 +11369,8 @@
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11314,6 +11502,8 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11445,6 +11635,8 @@
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11576,6 +11768,8 @@
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11707,6 +11901,8 @@
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11838,6 +12034,8 @@
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11969,6 +12167,8 @@
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12100,6 +12300,8 @@
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12231,6 +12433,8 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12362,6 +12566,8 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12493,6 +12699,8 @@
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12616,6 +12824,8 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12739,6 +12949,8 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12870,6 +13082,8 @@
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13001,6 +13215,8 @@
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -13132,6 +13348,8 @@
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13263,6 +13481,8 @@
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13394,6 +13614,8 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13525,6 +13747,8 @@
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13656,6 +13880,8 @@
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13787,6 +14013,8 @@
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13918,6 +14146,8 @@
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14049,6 +14279,8 @@
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14180,6 +14412,8 @@
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14311,6 +14545,8 @@
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14442,6 +14678,8 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14573,6 +14811,8 @@
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14704,6 +14944,8 @@
       <c r="AE111" t="inlineStr"/>
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14835,6 +15077,8 @@
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14966,6 +15210,8 @@
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -15097,6 +15343,8 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -15228,6 +15476,8 @@
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -15351,6 +15601,8 @@
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -15474,6 +15726,8 @@
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15597,6 +15851,8 @@
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15728,6 +15984,8 @@
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15859,6 +16117,8 @@
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15990,6 +16250,8 @@
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -16121,6 +16383,8 @@
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -16252,6 +16516,8 @@
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -16383,6 +16649,8 @@
       <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -16514,6 +16782,8 @@
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -16645,6 +16915,8 @@
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -16776,6 +17048,8 @@
       <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16907,6 +17181,8 @@
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -17038,6 +17314,8 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -17169,6 +17447,8 @@
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -17300,6 +17580,8 @@
       <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -17431,6 +17713,8 @@
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -17562,6 +17846,8 @@
       <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -17685,6 +17971,8 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -17808,6 +18096,8 @@
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17939,6 +18229,8 @@
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -18070,6 +18362,8 @@
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -18201,6 +18495,8 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -18332,6 +18628,8 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -18463,6 +18761,8 @@
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -18594,6 +18894,8 @@
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -18721,6 +19023,8 @@
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -18848,6 +19152,8 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18975,6 +19281,8 @@
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -19102,6 +19410,8 @@
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -19229,6 +19539,8 @@
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -19356,6 +19668,8 @@
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -19483,6 +19797,8 @@
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -19610,6 +19926,8 @@
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -19737,6 +20055,8 @@
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19864,6 +20184,8 @@
       <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19991,6 +20313,8 @@
       <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -20114,6 +20438,8 @@
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -20237,6 +20563,8 @@
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -20364,6 +20692,8 @@
       <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -20491,6 +20821,8 @@
       <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -20618,6 +20950,8 @@
       <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -20745,6 +21079,8 @@
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -20872,6 +21208,8 @@
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -20999,6 +21337,8 @@
       <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -21126,6 +21466,8 @@
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -21249,6 +21591,8 @@
       <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -21376,6 +21720,8 @@
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -21503,6 +21849,8 @@
       <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -21634,6 +21982,8 @@
       <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -21757,6 +22107,8 @@
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -21880,6 +22232,8 @@
       <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -22003,6 +22357,8 @@
       <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -22126,6 +22482,8 @@
       <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -22249,6 +22607,8 @@
       <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -22372,6 +22732,8 @@
       <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -22495,6 +22857,8 @@
       <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -22618,6 +22982,8 @@
       <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -22741,6 +23107,8 @@
       <c r="AE174" t="inlineStr"/>
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -22864,6 +23232,8 @@
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -22987,6 +23357,8 @@
       <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -23110,6 +23482,8 @@
       <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -23233,6 +23607,8 @@
       <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -23356,6 +23732,8 @@
       <c r="AE179" t="inlineStr"/>
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -23479,6 +23857,8 @@
       <c r="AE180" t="inlineStr"/>
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -23602,6 +23982,8 @@
       <c r="AE181" t="inlineStr"/>
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -23725,6 +24107,8 @@
       <c r="AE182" t="inlineStr"/>
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -23848,6 +24232,8 @@
       <c r="AE183" t="inlineStr"/>
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -23971,6 +24357,8 @@
       <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -24094,6 +24482,8 @@
       <c r="AE185" t="inlineStr"/>
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -24217,6 +24607,8 @@
       <c r="AE186" t="inlineStr"/>
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -24340,6 +24732,8 @@
       <c r="AE187" t="inlineStr"/>
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -24463,6 +24857,8 @@
       <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -24586,6 +24982,8 @@
       <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -24709,6 +25107,8 @@
       <c r="AE190" t="inlineStr"/>
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -24832,6 +25232,8 @@
       <c r="AE191" t="inlineStr"/>
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -24955,6 +25357,8 @@
       <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -25078,6 +25482,8 @@
       <c r="AE193" t="inlineStr"/>
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -25201,6 +25607,8 @@
       <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -25324,6 +25732,8 @@
       <c r="AE195" t="inlineStr"/>
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -25447,6 +25857,8 @@
       <c r="AE196" t="inlineStr"/>
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -25570,6 +25982,8 @@
       <c r="AE197" t="inlineStr"/>
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -25693,6 +26107,8 @@
       <c r="AE198" t="inlineStr"/>
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -25816,6 +26232,8 @@
       <c r="AE199" t="inlineStr"/>
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -25939,6 +26357,8 @@
       <c r="AE200" t="inlineStr"/>
       <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -26062,6 +26482,8 @@
       <c r="AE201" t="inlineStr"/>
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -26185,6 +26607,8 @@
       <c r="AE202" t="inlineStr"/>
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -26308,6 +26732,8 @@
       <c r="AE203" t="inlineStr"/>
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -26431,6 +26857,8 @@
       <c r="AE204" t="inlineStr"/>
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -26554,6 +26982,8 @@
       <c r="AE205" t="inlineStr"/>
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -26677,6 +27107,8 @@
       <c r="AE206" t="inlineStr"/>
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -26800,6 +27232,8 @@
       <c r="AE207" t="inlineStr"/>
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -26923,6 +27357,8 @@
       <c r="AE208" t="inlineStr"/>
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -27046,6 +27482,8 @@
       <c r="AE209" t="inlineStr"/>
       <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -27169,6 +27607,8 @@
       <c r="AE210" t="inlineStr"/>
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -27292,6 +27732,8 @@
       <c r="AE211" t="inlineStr"/>
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -27415,6 +27857,8 @@
       <c r="AE212" t="inlineStr"/>
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -27538,6 +27982,8 @@
       <c r="AE213" t="inlineStr"/>
       <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -27592,7 +28038,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>未整備</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -27639,7 +28085,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>2026-05-04 12:00:00</t>
+          <t>2026-05-05 17:58:33</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -27661,6 +28107,8 @@
       <c r="AE214" t="inlineStr"/>
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -27715,7 +28163,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>未整備</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -27762,7 +28210,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>2026-05-04 12:00:00</t>
+          <t>2026-05-05 17:57:13</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -27784,6 +28232,8 @@
       <c r="AE215" t="inlineStr"/>
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -27907,6 +28357,8 @@
       <c r="AE216" t="inlineStr"/>
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -28030,6 +28482,8 @@
       <c r="AE217" t="inlineStr"/>
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -28153,6 +28607,8 @@
       <c r="AE218" t="inlineStr"/>
       <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -28276,6 +28732,8 @@
       <c r="AE219" t="inlineStr"/>
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -28399,6 +28857,8 @@
       <c r="AE220" t="inlineStr"/>
       <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr"/>
+      <c r="AI220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -28522,6 +28982,8 @@
       <c r="AE221" t="inlineStr"/>
       <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
+      <c r="AI221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -28645,6 +29107,8 @@
       <c r="AE222" t="inlineStr"/>
       <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr"/>
+      <c r="AI222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -28768,6 +29232,8 @@
       <c r="AE223" t="inlineStr"/>
       <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr"/>
+      <c r="AI223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -28891,6 +29357,8 @@
       <c r="AE224" t="inlineStr"/>
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -29014,6 +29482,8 @@
       <c r="AE225" t="inlineStr"/>
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
+      <c r="AI225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -29137,6 +29607,8 @@
       <c r="AE226" t="inlineStr"/>
       <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr"/>
+      <c r="AI226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -29260,6 +29732,8 @@
       <c r="AE227" t="inlineStr"/>
       <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
+      <c r="AI227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -29314,7 +29788,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>未整備</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -29361,7 +29835,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>2026-05-04 12:00:00</t>
+          <t>2026-05-05 17:57:46</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -29383,6 +29857,8 @@
       <c r="AE228" t="inlineStr"/>
       <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr"/>
+      <c r="AI228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -29506,6 +29982,8 @@
       <c r="AE229" t="inlineStr"/>
       <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr"/>
+      <c r="AI229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -29629,6 +30107,8 @@
       <c r="AE230" t="inlineStr"/>
       <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr"/>
+      <c r="AI230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -29752,6 +30232,8 @@
       <c r="AE231" t="inlineStr"/>
       <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr"/>
+      <c r="AI231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -29875,6 +30357,8 @@
       <c r="AE232" t="inlineStr"/>
       <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -29998,6 +30482,8 @@
       <c r="AE233" t="inlineStr"/>
       <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr"/>
+      <c r="AI233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -30121,6 +30607,8 @@
       <c r="AE234" t="inlineStr"/>
       <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr"/>
+      <c r="AI234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -30244,6 +30732,8 @@
       <c r="AE235" t="inlineStr"/>
       <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="inlineStr"/>
+      <c r="AH235" t="inlineStr"/>
+      <c r="AI235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -30367,6 +30857,8 @@
       <c r="AE236" t="inlineStr"/>
       <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -30490,6 +30982,8 @@
       <c r="AE237" t="inlineStr"/>
       <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -30613,6 +31107,8 @@
       <c r="AE238" t="inlineStr"/>
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="inlineStr"/>
+      <c r="AH238" t="inlineStr"/>
+      <c r="AI238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -30736,6 +31232,8 @@
       <c r="AE239" t="inlineStr"/>
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr"/>
+      <c r="AI239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -30859,6 +31357,8 @@
       <c r="AE240" t="inlineStr"/>
       <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr"/>
+      <c r="AI240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -30982,6 +31482,8 @@
       <c r="AE241" t="inlineStr"/>
       <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
+      <c r="AI241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -31105,6 +31607,8 @@
       <c r="AE242" t="inlineStr"/>
       <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr"/>
+      <c r="AI242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -31228,6 +31732,8 @@
       <c r="AE243" t="inlineStr"/>
       <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr"/>
+      <c r="AI243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -31351,6 +31857,8 @@
       <c r="AE244" t="inlineStr"/>
       <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr"/>
+      <c r="AI244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -31474,6 +31982,8 @@
       <c r="AE245" t="inlineStr"/>
       <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -31597,6 +32107,8 @@
       <c r="AE246" t="inlineStr"/>
       <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr"/>
+      <c r="AI246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -31720,6 +32232,8 @@
       <c r="AE247" t="inlineStr"/>
       <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr"/>
+      <c r="AI247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -31843,6 +32357,8 @@
       <c r="AE248" t="inlineStr"/>
       <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr"/>
+      <c r="AI248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -31966,6 +32482,8 @@
       <c r="AE249" t="inlineStr"/>
       <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr"/>
+      <c r="AI249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -32089,6 +32607,8 @@
       <c r="AE250" t="inlineStr"/>
       <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr"/>
+      <c r="AI250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -32212,6 +32732,8 @@
       <c r="AE251" t="inlineStr"/>
       <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
+      <c r="AI251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -32335,6 +32857,8 @@
       <c r="AE252" t="inlineStr"/>
       <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="inlineStr"/>
+      <c r="AH252" t="inlineStr"/>
+      <c r="AI252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -32458,6 +32982,8 @@
       <c r="AE253" t="inlineStr"/>
       <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="inlineStr"/>
+      <c r="AH253" t="inlineStr"/>
+      <c r="AI253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -32581,6 +33107,8 @@
       <c r="AE254" t="inlineStr"/>
       <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
+      <c r="AI254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -32704,6 +33232,8 @@
       <c r="AE255" t="inlineStr"/>
       <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="inlineStr"/>
+      <c r="AH255" t="inlineStr"/>
+      <c r="AI255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -32827,6 +33357,8 @@
       <c r="AE256" t="inlineStr"/>
       <c r="AF256" t="inlineStr"/>
       <c r="AG256" t="inlineStr"/>
+      <c r="AH256" t="inlineStr"/>
+      <c r="AI256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -32950,6 +33482,8 @@
       <c r="AE257" t="inlineStr"/>
       <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="inlineStr"/>
+      <c r="AH257" t="inlineStr"/>
+      <c r="AI257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -33073,6 +33607,8 @@
       <c r="AE258" t="inlineStr"/>
       <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="inlineStr"/>
+      <c r="AH258" t="inlineStr"/>
+      <c r="AI258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -33196,6 +33732,8 @@
       <c r="AE259" t="inlineStr"/>
       <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="inlineStr"/>
+      <c r="AH259" t="inlineStr"/>
+      <c r="AI259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -33319,6 +33857,8 @@
       <c r="AE260" t="inlineStr"/>
       <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="inlineStr"/>
+      <c r="AH260" t="inlineStr"/>
+      <c r="AI260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -33442,6 +33982,433 @@
       <c r="AE261" t="inlineStr"/>
       <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="inlineStr"/>
+      <c r="AH261" t="inlineStr"/>
+      <c r="AI261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>COST-001</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>原価管理</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>製品別・案件別原価管理表</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>未整備</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>templates/documents/COST-001_product_project_cost_management.xlsx</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="inlineStr"/>
+      <c r="W262" t="inlineStr"/>
+      <c r="X262" t="inlineStr"/>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:06:09</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:28:52</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr"/>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr"/>
+      <c r="AE262" t="inlineStr"/>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>製品別・案件別に材料費、外注費、労務費、製造間接費を把握するための管理表。</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>COST-002</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>原価管理</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>原価分類ルール表</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>未整備</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>templates/documents/COST-002_cost_classification_rule.xlsx</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr"/>
+      <c r="U263" t="inlineStr"/>
+      <c r="V263" t="inlineStr"/>
+      <c r="W263" t="inlineStr"/>
+      <c r="X263" t="inlineStr"/>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:06:09</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:28:52</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr"/>
+      <c r="AB263" t="inlineStr"/>
+      <c r="AC263" t="inlineStr"/>
+      <c r="AD263" t="inlineStr"/>
+      <c r="AE263" t="inlineStr"/>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="inlineStr"/>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>材料費、外注費、労務費、製造間接費の分類ルールを定義するための表。</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>COST-003</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>原価管理</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>月次原価率・粗利率確認表</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>未整備</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>templates/documents/COST-003_monthly_cost_gross_profit_check.xlsx</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr"/>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr"/>
+      <c r="W264" t="inlineStr"/>
+      <c r="X264" t="inlineStr"/>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:06:09</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:28:52</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr"/>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
+      <c r="AD264" t="inlineStr"/>
+      <c r="AE264" t="inlineStr"/>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="inlineStr"/>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>月次で原価率、粗利率、前月差異、主な変動要因を確認するための表。</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>COST-004</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>原価管理</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>見積原価・実績原価比較表</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>製造部</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>未整備</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>templates/documents/COST-004_estimated_actual_cost_comparison.xlsx</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr"/>
+      <c r="U265" t="inlineStr"/>
+      <c r="V265" t="inlineStr"/>
+      <c r="W265" t="inlineStr"/>
+      <c r="X265" t="inlineStr"/>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:06:09</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:28:52</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr"/>
+      <c r="AB265" t="inlineStr"/>
+      <c r="AC265" t="inlineStr"/>
+      <c r="AD265" t="inlineStr"/>
+      <c r="AE265" t="inlineStr"/>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="inlineStr"/>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>見積時の原価と実績原価を比較し、差異理由を確認するための表。</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>COST-005</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>原価管理</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>不良・手直し・歩留まりロス管理表</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>製造部</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>製造部</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>未整備</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>templates/documents/COST-005_defect_rework_yield_loss_management.xlsx</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr"/>
+      <c r="W266" t="inlineStr"/>
+      <c r="X266" t="inlineStr"/>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:06:09</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:28:52</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr"/>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr"/>
+      <c r="AD266" t="inlineStr"/>
+      <c r="AE266" t="inlineStr"/>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>不良、手直し、歩留まりロスが原価に与える影響を把握するための管理表。</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
